--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. GETAFE.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. GETAFE.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>38.2732</v>
+        <v>30.9932</v>
       </c>
       <c r="E2" t="n">
-        <v>27.2749</v>
+        <v>45.5223</v>
       </c>
       <c r="F2" t="n">
-        <v>10.998</v>
+        <v>-14.5298</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2818</v>
+        <v>30.1039</v>
       </c>
       <c r="H2" t="n">
-        <v>9.739700000000001</v>
+        <v>10.6688</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.4581</v>
+        <v>19.435</v>
       </c>
       <c r="J2" t="n">
-        <v>35.0368</v>
+        <v>71.38030000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>26.2498</v>
+        <v>32.8931</v>
       </c>
       <c r="L2" t="n">
-        <v>8.786900000000001</v>
+        <v>38.4871</v>
       </c>
       <c r="M2" t="n">
-        <v>-32.755</v>
+        <v>-41.2765</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.5102</v>
+        <v>-22.2246</v>
       </c>
       <c r="O2" t="n">
-        <v>-16.2448</v>
+        <v>-19.0518</v>
       </c>
       <c r="P2" t="n">
-        <v>-31.8281</v>
+        <v>-7.1866</v>
       </c>
       <c r="Q2" t="n">
-        <v>-69.4055</v>
+        <v>-42.9166</v>
       </c>
       <c r="R2" t="n">
-        <v>37.5777</v>
+        <v>35.7298</v>
       </c>
       <c r="S2" t="n">
-        <v>48.1236</v>
+        <v>-3.4027</v>
       </c>
       <c r="T2" t="n">
-        <v>25.9958</v>
+        <v>-4.3782</v>
       </c>
       <c r="U2" t="n">
-        <v>22.128</v>
+        <v>0.9753999999999998</v>
       </c>
       <c r="V2" t="n">
-        <v>19.6958</v>
+        <v>11.4786</v>
       </c>
       <c r="W2" t="n">
-        <v>35.6482</v>
+        <v>21.4367</v>
       </c>
       <c r="X2" t="n">
-        <v>-15.9521</v>
+        <v>-9.9581</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>13.2639</v>
+        <v>21.311</v>
       </c>
       <c r="E3" t="n">
-        <v>17.5346</v>
+        <v>22.9506</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.2707</v>
+        <v>-1.6396</v>
       </c>
       <c r="G3" t="n">
         <v>13.5595</v>
@@ -688,13 +688,13 @@
         <v>21.1503</v>
       </c>
       <c r="S3" t="n">
-        <v>-8.3733</v>
+        <v>-0.3263000000000003</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.9645</v>
+        <v>-0.5485000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.4089</v>
+        <v>0.2221000000000002</v>
       </c>
       <c r="V3" t="n">
         <v>9.104700000000001</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>10.2101</v>
+        <v>8.026599999999998</v>
       </c>
       <c r="E4" t="n">
-        <v>34.41500000000001</v>
+        <v>8.097899999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-24.2048</v>
+        <v>-0.07060000000000033</v>
       </c>
       <c r="G4" t="n">
-        <v>30.1039</v>
+        <v>2.2818</v>
       </c>
       <c r="H4" t="n">
-        <v>10.6688</v>
+        <v>9.739700000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>19.435</v>
+        <v>-7.4581</v>
       </c>
       <c r="J4" t="n">
-        <v>71.38030000000001</v>
+        <v>35.0368</v>
       </c>
       <c r="K4" t="n">
-        <v>32.8931</v>
+        <v>26.2498</v>
       </c>
       <c r="L4" t="n">
-        <v>38.4871</v>
+        <v>8.786900000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-41.2765</v>
+        <v>-32.755</v>
       </c>
       <c r="N4" t="n">
-        <v>-22.2246</v>
+        <v>-16.5102</v>
       </c>
       <c r="O4" t="n">
-        <v>-19.0518</v>
+        <v>-16.2448</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.1866</v>
+        <v>-31.8281</v>
       </c>
       <c r="Q4" t="n">
-        <v>-42.9166</v>
+        <v>-69.4055</v>
       </c>
       <c r="R4" t="n">
-        <v>35.7298</v>
+        <v>37.5777</v>
       </c>
       <c r="S4" t="n">
-        <v>-24.1852</v>
+        <v>17.877</v>
       </c>
       <c r="T4" t="n">
-        <v>-15.4857</v>
+        <v>6.8187</v>
       </c>
       <c r="U4" t="n">
-        <v>-8.6996</v>
+        <v>11.0589</v>
       </c>
       <c r="V4" t="n">
-        <v>11.4786</v>
+        <v>19.6958</v>
       </c>
       <c r="W4" t="n">
-        <v>21.4367</v>
+        <v>35.6482</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.9581</v>
+        <v>-15.9521</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>10.1947</v>
+        <v>7.1918</v>
       </c>
       <c r="E5" t="n">
-        <v>11.6563</v>
+        <v>9.420900000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4617</v>
+        <v>-2.2291</v>
       </c>
       <c r="G5" t="n">
         <v>-5.1167</v>
@@ -844,13 +844,13 @@
         <v>5.133599999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>7.4077</v>
+        <v>4.4051</v>
       </c>
       <c r="T5" t="n">
-        <v>4.9505</v>
+        <v>2.7152</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4572</v>
+        <v>1.6899</v>
       </c>
       <c r="V5" t="n">
         <v>4.8233</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>G. KASANZI OBAMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>7.020100000000001</v>
+        <v>5.668899999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>11.5367</v>
+        <v>0.1178000000000003</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.5167</v>
+        <v>5.5512</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5059</v>
+        <v>1.7817</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2584</v>
+        <v>-2.494499999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.7524</v>
+        <v>4.276199999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>18.424</v>
+        <v>7.8767</v>
       </c>
       <c r="K6" t="n">
-        <v>14.8987</v>
+        <v>6.0376</v>
       </c>
       <c r="L6" t="n">
-        <v>3.5256</v>
+        <v>1.8394</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.9183</v>
+        <v>-6.095</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.6399</v>
+        <v>-8.532</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.2781</v>
+        <v>2.4367</v>
       </c>
       <c r="P6" t="n">
-        <v>-17.4542</v>
+        <v>0.4106000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-38.1934</v>
+        <v>-13.5525</v>
       </c>
       <c r="R6" t="n">
-        <v>20.7397</v>
+        <v>13.9631</v>
       </c>
       <c r="S6" t="n">
-        <v>32.6315</v>
+        <v>1.7949</v>
       </c>
       <c r="T6" t="n">
-        <v>23.9907</v>
+        <v>0.0953999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>8.640700000000001</v>
+        <v>1.6995</v>
       </c>
       <c r="V6" t="n">
-        <v>-8.663</v>
+        <v>1.6816</v>
       </c>
       <c r="W6" t="n">
-        <v>7.315700000000001</v>
+        <v>5.6979</v>
       </c>
       <c r="X6" t="n">
-        <v>-15.9789</v>
+        <v>-4.0162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. KASANZI OBAMA</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5418</v>
+        <v>4.071700000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1143</v>
+        <v>14.2406</v>
       </c>
       <c r="F7" t="n">
-        <v>3.656</v>
+        <v>-10.1689</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7817</v>
+        <v>23.4424</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.494499999999999</v>
+        <v>11.7289</v>
       </c>
       <c r="I7" t="n">
-        <v>4.276199999999999</v>
+        <v>11.7137</v>
       </c>
       <c r="J7" t="n">
-        <v>7.8767</v>
+        <v>58.5356</v>
       </c>
       <c r="K7" t="n">
-        <v>6.0376</v>
+        <v>33.9273</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8394</v>
+        <v>24.6079</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.095</v>
+        <v>-35.0928</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.532</v>
+        <v>-22.1981</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4367</v>
+        <v>-12.8947</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4106000000000001</v>
+        <v>-32.2388</v>
       </c>
       <c r="Q7" t="n">
-        <v>-13.5525</v>
+        <v>-72.48560000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>13.9631</v>
+        <v>40.2469</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3322</v>
+        <v>4.0729</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1366</v>
+        <v>2.1035</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1958</v>
+        <v>1.9696</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6816</v>
+        <v>8.7944</v>
       </c>
       <c r="W7" t="n">
-        <v>5.6979</v>
+        <v>26.0874</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.0162</v>
+        <v>-17.2927</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>1.260300000000001</v>
+        <v>3.440499999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.749900000000001</v>
+        <v>-0.5806000000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>5.009799999999999</v>
+        <v>4.0212</v>
       </c>
       <c r="G8" t="n">
         <v>-5.2187</v>
@@ -1078,13 +1078,13 @@
         <v>26.8999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3838999999999996</v>
+        <v>2.564299999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8551000000000002</v>
+        <v>2.3142</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2388</v>
+        <v>0.2499999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-4.788</v>
@@ -1111,13 +1111,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4387</v>
+        <v>0.4684</v>
       </c>
       <c r="E9" t="n">
         <v>-0.7508</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1895</v>
+        <v>1.2192</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9526</v>
@@ -1156,13 +1156,13 @@
         <v>1.232</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1593</v>
+        <v>0.1889</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0504</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2097</v>
+        <v>0.2393</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6797</v>
+        <v>0.06549999999999945</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8657999999999999</v>
+        <v>2.4621</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.5457</v>
+        <v>-2.3966</v>
       </c>
       <c r="G10" t="n">
         <v>0.1327</v>
@@ -1234,13 +1234,13 @@
         <v>8.418900000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.1349</v>
+        <v>0.6102000000000002</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4697000000000001</v>
+        <v>1.1265</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.6653</v>
+        <v>-0.5165</v>
       </c>
       <c r="V10" t="n">
         <v>-5.1949</v>
@@ -1267,13 +1267,13 @@
         <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.476099999999999</v>
+        <v>-3.000900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4551</v>
+        <v>7.4277</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.9312</v>
+        <v>-10.4285</v>
       </c>
       <c r="G11" t="n">
         <v>-3.253699999999998</v>
@@ -1312,13 +1312,13 @@
         <v>27.1051</v>
       </c>
       <c r="S11" t="n">
-        <v>3.997199999999999</v>
+        <v>6.4727</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.9558</v>
+        <v>-1.9829</v>
       </c>
       <c r="U11" t="n">
-        <v>6.9531</v>
+        <v>8.4556</v>
       </c>
       <c r="V11" t="n">
         <v>-5.1928</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>I. IBAÑEZ ZAMALLOA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.942599999999999</v>
+        <v>-4.9392</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3153</v>
+        <v>-4.8107</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.6272</v>
+        <v>-0.1285000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.2828</v>
+        <v>-3.8155</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.5797</v>
+        <v>-1.7815</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.7032</v>
+        <v>-2.0338</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4826</v>
+        <v>0.002100000000000019</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2916</v>
+        <v>0.06870000000000007</v>
       </c>
       <c r="L12" t="n">
-        <v>3.7739</v>
+        <v>-0.06659999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-13.7652</v>
+        <v>-3.8175</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.2885</v>
+        <v>-1.8504</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.4772</v>
+        <v>-1.9671</v>
       </c>
       <c r="P12" t="n">
-        <v>8.2135</v>
+        <v>-1.232</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.008199999999999</v>
+        <v>-5.1335</v>
       </c>
       <c r="R12" t="n">
-        <v>16.2219</v>
+        <v>3.9015</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4079</v>
+        <v>1.5662</v>
       </c>
       <c r="T12" t="n">
-        <v>1.49</v>
+        <v>0.6698</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9183000000000003</v>
+        <v>0.8963</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.2813</v>
+        <v>-1.4579</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7206</v>
+        <v>-0.3491</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.001900000000001</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. IBAÑEZ ZAMALLOA</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.521</v>
+        <v>-5.763700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8181</v>
+        <v>-3.097799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7029</v>
+        <v>-2.6661</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.8155</v>
+        <v>-10.2828</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7815</v>
+        <v>-6.5797</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.0338</v>
+        <v>-3.7032</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002100000000000019</v>
+        <v>3.4826</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06870000000000007</v>
+        <v>-0.2916</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.06659999999999999</v>
+        <v>3.7739</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.8175</v>
+        <v>-13.7652</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8504</v>
+        <v>-6.2885</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.9671</v>
+        <v>-7.4772</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.232</v>
+        <v>8.2135</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.1335</v>
+        <v>-8.008199999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9015</v>
+        <v>16.2219</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0156</v>
+        <v>3.5867</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3374</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.678</v>
+        <v>2.8795</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4579</v>
+        <v>-7.2813</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3491</v>
+        <v>0.7206</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1088</v>
+        <v>-8.001900000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.0238</v>
+        <v>-10.2523</v>
       </c>
       <c r="E14" t="n">
-        <v>7.096500000000002</v>
+        <v>-2.684800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.1206</v>
+        <v>-7.5671</v>
       </c>
       <c r="G14" t="n">
-        <v>23.4424</v>
+        <v>0.5059</v>
       </c>
       <c r="H14" t="n">
-        <v>11.7289</v>
+        <v>4.2584</v>
       </c>
       <c r="I14" t="n">
-        <v>11.7137</v>
+        <v>-3.7524</v>
       </c>
       <c r="J14" t="n">
-        <v>58.5356</v>
+        <v>18.424</v>
       </c>
       <c r="K14" t="n">
-        <v>33.9273</v>
+        <v>14.8987</v>
       </c>
       <c r="L14" t="n">
-        <v>24.6079</v>
+        <v>3.5256</v>
       </c>
       <c r="M14" t="n">
-        <v>-35.0928</v>
+        <v>-17.9183</v>
       </c>
       <c r="N14" t="n">
-        <v>-22.1981</v>
+        <v>-10.6399</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.8947</v>
+        <v>-7.2781</v>
       </c>
       <c r="P14" t="n">
-        <v>-32.2388</v>
+        <v>-17.4542</v>
       </c>
       <c r="Q14" t="n">
-        <v>-72.48560000000001</v>
+        <v>-38.1934</v>
       </c>
       <c r="R14" t="n">
-        <v>40.2469</v>
+        <v>20.7397</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.0224</v>
+        <v>15.3592</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.0408</v>
+        <v>9.768599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.9816</v>
+        <v>5.5906</v>
       </c>
       <c r="V14" t="n">
-        <v>8.7944</v>
+        <v>-8.663</v>
       </c>
       <c r="W14" t="n">
-        <v>26.0874</v>
+        <v>7.315700000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-17.2927</v>
+        <v>-15.9789</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.8669</v>
+        <v>-15.3484</v>
       </c>
       <c r="E15" t="n">
-        <v>-18.2459</v>
+        <v>-14.2282</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.620800000000001</v>
+        <v>-1.1202</v>
       </c>
       <c r="G15" t="n">
         <v>8.0167</v>
@@ -1624,13 +1624,13 @@
         <v>27.3105</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.025600000000001</v>
+        <v>1.4928</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.315</v>
+        <v>0.7026</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.7106</v>
+        <v>0.7905000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-10.0733</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-47.5003</v>
+        <v>-33.352</v>
       </c>
       <c r="E16" t="n">
-        <v>-29.9463</v>
+        <v>-22.6048</v>
       </c>
       <c r="F16" t="n">
-        <v>-17.5541</v>
+        <v>-10.7475</v>
       </c>
       <c r="G16" t="n">
         <v>-37.7193</v>
@@ -1702,13 +1702,13 @@
         <v>41.8897</v>
       </c>
       <c r="S16" t="n">
-        <v>-13.7647</v>
+        <v>0.3836999999999997</v>
       </c>
       <c r="T16" t="n">
-        <v>-9.732800000000001</v>
+        <v>-2.3909</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.0322</v>
+        <v>2.775</v>
       </c>
       <c r="V16" t="n">
         <v>7.6797</v>
@@ -1735,22 +1735,22 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-23.80759999999999</v>
+        <v>8.581100000000006</v>
       </c>
       <c r="E17" t="n">
-        <v>54.89430000000002</v>
+        <v>61.48220000000003</v>
       </c>
       <c r="F17" t="n">
-        <v>-78.70310000000001</v>
+        <v>-52.90089999999999</v>
       </c>
       <c r="G17" t="n">
         <v>13.46530000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>8.729400000000002</v>
+        <v>8.729399999999998</v>
       </c>
       <c r="I17" t="n">
-        <v>4.735599999999994</v>
+        <v>4.735599999999998</v>
       </c>
       <c r="J17" t="n">
         <v>298.3889</v>
@@ -1777,19 +1777,19 @@
         <v>-409.6565</v>
       </c>
       <c r="R17" t="n">
-        <v>327.5206</v>
+        <v>327.5205999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>24.2572</v>
+        <v>56.6456</v>
       </c>
       <c r="T17" t="n">
-        <v>11.08319999999999</v>
+        <v>17.6708</v>
       </c>
       <c r="U17" t="n">
-        <v>13.1738</v>
+        <v>38.9757</v>
       </c>
       <c r="V17" t="n">
-        <v>20.6069</v>
+        <v>20.60690000000001</v>
       </c>
       <c r="W17" t="n">
         <v>155.079</v>
